--- a/files/九龙-九龙塘-The Monet 第2期.xlsx
+++ b/files/九龙-九龙塘-The Monet 第2期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,65 +39,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -109,36 +51,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -168,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -178,39 +90,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1386,319 +1265,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Monet 第2期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-九龙塘-The Monet 第2期.xlsx
+++ b/files/九龙-九龙塘-The Monet 第2期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,85 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +129,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -90,6 +198,51 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1265,4 +1418,319 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-九龙塘-The Monet 第2期.xlsx
+++ b/files/九龙-九龙塘-The Monet 第2期.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -622,6 +622,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -679,6 +683,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -731,6 +755,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -783,6 +827,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -835,6 +899,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -887,6 +971,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -939,6 +1043,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -991,6 +1115,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1043,6 +1187,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1095,6 +1259,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1147,6 +1331,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1199,6 +1403,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1251,6 +1475,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1303,6 +1547,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1355,6 +1619,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1407,13 +1691,33 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
